--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.69718209293364</v>
+        <v>7.750792090101718</v>
       </c>
       <c r="D2" t="n">
-        <v>47.299044927692</v>
+        <v>7.686094800749951</v>
       </c>
       <c r="E2" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F2" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.40702370249939</v>
+        <v>6.891141351656151</v>
       </c>
       <c r="D3" t="n">
-        <v>42.57329667073081</v>
+        <v>6.918160708993756</v>
       </c>
       <c r="E3" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F3" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.17075067311509</v>
+        <v>5.715246984381203</v>
       </c>
       <c r="D4" t="n">
-        <v>35.89510822557187</v>
+        <v>5.832955086655429</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F4" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.43074526132705</v>
+        <v>8.519996104965646</v>
       </c>
       <c r="D5" t="n">
-        <v>50.85593556333925</v>
+        <v>8.264089529042629</v>
       </c>
       <c r="E5" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F5" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.54400255102014</v>
+        <v>2.038400414540773</v>
       </c>
       <c r="D6" t="n">
-        <v>12.18198314874821</v>
+        <v>1.979572261671584</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F6" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.36936957566098</v>
+        <v>4.93502255604491</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00935722920572</v>
+        <v>4.87652054974593</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F7" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.04793242595711</v>
+        <v>2.77028901921803</v>
       </c>
       <c r="D8" t="n">
-        <v>16.89686839956586</v>
+        <v>2.745741114929453</v>
       </c>
       <c r="E8" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F8" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.05293361728251</v>
+        <v>7.483601712808407</v>
       </c>
       <c r="D9" t="n">
-        <v>43.62792057046061</v>
+        <v>7.08953709269985</v>
       </c>
       <c r="E9" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F9" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.82071507656021</v>
+        <v>4.033366199941034</v>
       </c>
       <c r="D10" t="n">
-        <v>23.68881947967719</v>
+        <v>3.849433165447543</v>
       </c>
       <c r="E10" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F10" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.86237992458047</v>
+        <v>6.802636737744328</v>
       </c>
       <c r="D11" t="n">
-        <v>43.13376175447208</v>
+        <v>7.009236285101712</v>
       </c>
       <c r="E11" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F11" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.70640799105835</v>
+        <v>2.552291298546981</v>
       </c>
       <c r="D12" t="n">
-        <v>12.88162779673516</v>
+        <v>2.093264516969463</v>
       </c>
       <c r="E12" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F12" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>3.333531547117055</v>
+        <v>0.5416988764065215</v>
       </c>
       <c r="D13" t="n">
-        <v>7.138002570541321</v>
+        <v>1.159925417712965</v>
       </c>
       <c r="E13" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F13" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.92517322224121</v>
+        <v>5.025340648614197</v>
       </c>
       <c r="D14" t="n">
-        <v>27.34701706203637</v>
+        <v>4.44389027258091</v>
       </c>
       <c r="E14" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F14" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.86686914165239</v>
+        <v>5.828366235518513</v>
       </c>
       <c r="D15" t="n">
-        <v>38.98137998138786</v>
+        <v>6.334474246975527</v>
       </c>
       <c r="E15" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F15" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>54.58780148363871</v>
+        <v>8.870517741091291</v>
       </c>
       <c r="D16" t="n">
-        <v>51.28912863126578</v>
+        <v>8.334483402580689</v>
       </c>
       <c r="E16" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F16" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>51.73430450269804</v>
+        <v>8.406824481688433</v>
       </c>
       <c r="D17" t="n">
-        <v>51.63905573173891</v>
+        <v>8.391346556407573</v>
       </c>
       <c r="E17" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F17" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>64.96489615720837</v>
+        <v>10.55679562554636</v>
       </c>
       <c r="D18" t="n">
-        <v>61.63117204835049</v>
+        <v>10.01506545785695</v>
       </c>
       <c r="E18" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F18" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>53.61635567986036</v>
+        <v>8.712657797977309</v>
       </c>
       <c r="D19" t="n">
-        <v>52.39012009065089</v>
+        <v>8.51339451473077</v>
       </c>
       <c r="E19" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F19" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>58.42483017932041</v>
+        <v>9.494034904139566</v>
       </c>
       <c r="D20" t="n">
-        <v>56.48222787910209</v>
+        <v>9.178362030354091</v>
       </c>
       <c r="E20" t="n">
-        <v>16.75424270335783</v>
+        <v>2.722564439295647</v>
       </c>
       <c r="F20" t="n">
-        <v>16.00935999997314</v>
+        <v>2.601520999995635</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
